--- a/digital-products/mdw-tco-planner/singapore-mdw-tco-planner-2026.xlsx
+++ b/digital-products/mdw-tco-planner/singapore-mdw-tco-planner-2026.xlsx
@@ -667,7 +667,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="S$#,##0"/>
+    <numFmt numFmtId="164" formatCode="&quot;S$&quot;#,##0"/>
     <numFmt numFmtId="165" formatCode="0.0%"/>
   </numFmts>
   <fonts count="15" x14ac:knownFonts="1">
@@ -2638,7 +2638,7 @@
         <v>25</v>
       </c>
       <c r="G13" s="13">
-        <f>'PROFILE &amp; INPUTS'!C22+PROFILE &amp; INPUTS'!C23</f>
+        <f>'PROFILE &amp; INPUTS'!C22+'PROFILE &amp; INPUTS'!C23</f>
         <v>0</v>
       </c>
       <c r="H13" s="9" t="s">
@@ -2709,7 +2709,7 @@
         <v>25</v>
       </c>
       <c r="G16" s="13">
-        <f>'PROFILE &amp; INPUTS'!C10+PROFILE &amp; INPUTS'!C11+PROFILE &amp; INPUTS'!C12+PROFILE &amp; INPUTS'!C13</f>
+        <f>'PROFILE &amp; INPUTS'!C10+'PROFILE &amp; INPUTS'!C11+'PROFILE &amp; INPUTS'!C12+'PROFILE &amp; INPUTS'!C13</f>
         <v>0</v>
       </c>
       <c r="H16" s="9" t="s">
